--- a/dataset_t6_grouped/results2/G4/G4_T1936_W0015F0002T0006Z000C1N6_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T1936_W0015F0002T0006Z000C1N6_analysis.xlsx
@@ -480,10 +480,10 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>37.60123512607403</v>
+        <v>6.11020070798703</v>
       </c>
       <c r="D2" t="n">
-        <v>37.70793372042729</v>
+        <v>6.127539229569435</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
